--- a/Main_Project/ResNet/Results/Experimento 6 - ResNet/training_metrics.xlsx
+++ b/Main_Project/ResNet/Results/Experimento 6 - ResNet/training_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Main_Project\ResNet\Results\Experimento 6 - ResNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598D0FBF-EE5C-4EB4-B9E8-275404C2A1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1303329A-20ED-4524-AB53-FD2EC1DCE264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="2235" windowWidth="21600" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="7">
   <si>
     <t>epoch</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>lr</t>
-  </si>
-  <si>
-    <t>top1</t>
   </si>
   <si>
     <t>val_accuracy</t>
@@ -57,12 +54,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -77,8 +80,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,33 +389,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:F201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -417,22 +426,19 @@
         <v>0.44761559367179998</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>0.1</v>
       </c>
       <c r="E2">
-        <v>0.44761559367179998</v>
-      </c>
-      <c r="F2">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -440,22 +446,19 @@
         <v>0.45272594690322998</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>0.1</v>
       </c>
       <c r="E3">
-        <v>0.45272594690322998</v>
-      </c>
-      <c r="F3">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -463,22 +466,19 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>0.1</v>
       </c>
       <c r="E4">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F4">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -486,22 +486,19 @@
         <v>0.45263537764549</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>0.1</v>
       </c>
       <c r="E5">
-        <v>0.45263537764549</v>
-      </c>
-      <c r="F5">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -509,22 +506,19 @@
         <v>0.45299765467643999</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>0.1</v>
       </c>
       <c r="E6">
-        <v>0.45299765467643999</v>
-      </c>
-      <c r="F6">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -532,22 +526,19 @@
         <v>0.45254483819008001</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>0.1</v>
       </c>
       <c r="E7">
-        <v>0.45254483819008001</v>
-      </c>
-      <c r="F7">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -555,22 +546,19 @@
         <v>0.45254483819008001</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>0.1</v>
       </c>
       <c r="E8">
-        <v>0.45254483819008001</v>
-      </c>
-      <c r="F8">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -578,22 +566,19 @@
         <v>0.45471835136414002</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>0.1</v>
       </c>
       <c r="E9">
-        <v>0.45471835136414002</v>
-      </c>
-      <c r="F9">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -601,22 +586,19 @@
         <v>0.45037129521370001</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>0.1</v>
       </c>
       <c r="E10">
-        <v>0.45037129521370001</v>
-      </c>
-      <c r="F10">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -624,22 +606,19 @@
         <v>0.45517116785049</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>0.1</v>
       </c>
       <c r="E11">
-        <v>0.45517116785049</v>
-      </c>
-      <c r="F11">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -647,22 +626,19 @@
         <v>0.45254483819008001</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>0.1</v>
       </c>
       <c r="E12">
-        <v>0.45254483819008001</v>
-      </c>
-      <c r="F12">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -670,22 +646,19 @@
         <v>0.45209202170371998</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13">
         <v>0.1</v>
       </c>
       <c r="E13">
-        <v>0.45209202170371998</v>
-      </c>
-      <c r="F13">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -693,22 +666,19 @@
         <v>0.45236369967460999</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>0.1</v>
       </c>
       <c r="E14">
-        <v>0.45236369967460999</v>
-      </c>
-      <c r="F14">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -716,22 +686,19 @@
         <v>0.45272594690322998</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>0.1</v>
       </c>
       <c r="E15">
-        <v>0.45272594690322998</v>
-      </c>
-      <c r="F15">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -739,22 +706,19 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>0.1</v>
       </c>
       <c r="E16">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F16">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -762,22 +726,19 @@
         <v>0.45236369967460999</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>0.1</v>
       </c>
       <c r="E17">
-        <v>0.45236369967460999</v>
-      </c>
-      <c r="F17">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -785,22 +746,19 @@
         <v>0.45480892062187001</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>0.1</v>
       </c>
       <c r="E18">
-        <v>0.45480892062187001</v>
-      </c>
-      <c r="F18">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -808,22 +766,19 @@
         <v>0.45326933264732</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>0.1</v>
       </c>
       <c r="E19">
-        <v>0.45326933264732</v>
-      </c>
-      <c r="F19">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -831,22 +786,19 @@
         <v>0.45290708541870001</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>0.1</v>
       </c>
       <c r="E20">
-        <v>0.45290708541870001</v>
-      </c>
-      <c r="F20">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -854,22 +806,19 @@
         <v>0.45118638873099998</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>0.1</v>
       </c>
       <c r="E21">
-        <v>0.45118638873099998</v>
-      </c>
-      <c r="F21">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -877,22 +826,19 @@
         <v>0.45172974467277999</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>0.1</v>
       </c>
       <c r="E22">
-        <v>0.45172974467277999</v>
-      </c>
-      <c r="F22">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -900,22 +846,19 @@
         <v>0.45589566230773998</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>0.1</v>
       </c>
       <c r="E23">
-        <v>0.45589566230773998</v>
-      </c>
-      <c r="F23">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -923,22 +866,19 @@
         <v>0.45281651616096003</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>0.1</v>
       </c>
       <c r="E24">
-        <v>0.45281651616096003</v>
-      </c>
-      <c r="F24">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -946,22 +886,19 @@
         <v>0.45091468095779003</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>0.1</v>
       </c>
       <c r="E25">
-        <v>0.45091468095779003</v>
-      </c>
-      <c r="F25">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -969,22 +906,19 @@
         <v>0.45091468095779003</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>0.1</v>
       </c>
       <c r="E26">
-        <v>0.45091468095779003</v>
-      </c>
-      <c r="F26">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -992,22 +926,19 @@
         <v>0.45571455359459001</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>0.1</v>
       </c>
       <c r="E27">
-        <v>0.45571455359459001</v>
-      </c>
-      <c r="F27">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1015,22 +946,19 @@
         <v>0.45471835136414002</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>0.1</v>
       </c>
       <c r="E28">
-        <v>0.45471835136414002</v>
-      </c>
-      <c r="F28">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1038,22 +966,19 @@
         <v>0.45136749744415</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>0.1</v>
       </c>
       <c r="E29">
-        <v>0.45136749744415</v>
-      </c>
-      <c r="F29">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1061,22 +986,19 @@
         <v>0.44973737001419001</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>0.1</v>
       </c>
       <c r="E30">
-        <v>0.44973737001419001</v>
-      </c>
-      <c r="F30">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1084,22 +1006,19 @@
         <v>0.45462778210639998</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>0.1</v>
       </c>
       <c r="E31">
-        <v>0.45462778210639998</v>
-      </c>
-      <c r="F31">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1107,22 +1026,19 @@
         <v>0.45517116785049</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>0.01</v>
       </c>
       <c r="E32">
-        <v>0.45517116785049</v>
-      </c>
-      <c r="F32">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1130,22 +1046,19 @@
         <v>0.45218256115913003</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>0.01</v>
       </c>
       <c r="E33">
-        <v>0.45218256115913003</v>
-      </c>
-      <c r="F33">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1153,22 +1066,19 @@
         <v>0.45345047116280002</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>0.01</v>
       </c>
       <c r="E34">
-        <v>0.45345047116280002</v>
-      </c>
-      <c r="F34">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1176,22 +1086,19 @@
         <v>0.45209202170371998</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>0.01</v>
       </c>
       <c r="E35">
-        <v>0.45209202170371998</v>
-      </c>
-      <c r="F35">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G35" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1199,22 +1106,19 @@
         <v>0.45390328764915</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D36">
         <v>0.01</v>
       </c>
       <c r="E36">
-        <v>0.45390328764915</v>
-      </c>
-      <c r="F36">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1222,22 +1126,19 @@
         <v>0.45254483819008001</v>
       </c>
       <c r="C37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>0.01</v>
       </c>
       <c r="E37">
-        <v>0.45254483819008001</v>
-      </c>
-      <c r="F37">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G37" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1245,22 +1146,19 @@
         <v>0.45209202170371998</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>0.01</v>
       </c>
       <c r="E38">
-        <v>0.45209202170371998</v>
-      </c>
-      <c r="F38">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1268,22 +1166,19 @@
         <v>0.45453721284866</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>0.01</v>
       </c>
       <c r="E39">
-        <v>0.45453721284866</v>
-      </c>
-      <c r="F39">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1291,22 +1186,19 @@
         <v>0.44919398427009999</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40">
         <v>0.01</v>
       </c>
       <c r="E40">
-        <v>0.44919398427009999</v>
-      </c>
-      <c r="F40">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1314,22 +1206,19 @@
         <v>0.45652961730956998</v>
       </c>
       <c r="C41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41">
         <v>0.01</v>
       </c>
       <c r="E41">
-        <v>0.45652961730956998</v>
-      </c>
-      <c r="F41">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1337,22 +1226,19 @@
         <v>0.45363157987594999</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D42">
         <v>0.01</v>
       </c>
       <c r="E42">
-        <v>0.45363157987594999</v>
-      </c>
-      <c r="F42">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G42" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1360,22 +1246,19 @@
         <v>0.45172974467277999</v>
       </c>
       <c r="C43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D43">
         <v>0.01</v>
       </c>
       <c r="E43">
-        <v>0.45172974467277999</v>
-      </c>
-      <c r="F43">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G43" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1383,22 +1266,19 @@
         <v>0.45091468095779003</v>
       </c>
       <c r="C44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44">
         <v>0.01</v>
       </c>
       <c r="E44">
-        <v>0.45091468095779003</v>
-      </c>
-      <c r="F44">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G44" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1406,22 +1286,19 @@
         <v>0.45499002933501997</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45">
         <v>0.01</v>
       </c>
       <c r="E45">
-        <v>0.45499002933501997</v>
-      </c>
-      <c r="F45">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G45" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1429,22 +1306,19 @@
         <v>0.45227313041687001</v>
       </c>
       <c r="C46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D46">
         <v>0.01</v>
       </c>
       <c r="E46">
-        <v>0.45227313041687001</v>
-      </c>
-      <c r="F46">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G46" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1452,22 +1326,19 @@
         <v>0.45254483819008001</v>
       </c>
       <c r="C47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47">
         <v>0.01</v>
       </c>
       <c r="E47">
-        <v>0.45254483819008001</v>
-      </c>
-      <c r="F47">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G47" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1475,22 +1346,19 @@
         <v>0.45335990190505998</v>
       </c>
       <c r="C48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D48">
         <v>0.01</v>
       </c>
       <c r="E48">
-        <v>0.45335990190505998</v>
-      </c>
-      <c r="F48">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G48" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1498,22 +1366,19 @@
         <v>0.45272594690322998</v>
       </c>
       <c r="C49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D49">
         <v>0.01</v>
       </c>
       <c r="E49">
-        <v>0.45272594690322998</v>
-      </c>
-      <c r="F49">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G49" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1521,22 +1386,19 @@
         <v>0.45290708541870001</v>
       </c>
       <c r="C50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50">
         <v>0.01</v>
       </c>
       <c r="E50">
-        <v>0.45290708541870001</v>
-      </c>
-      <c r="F50">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G50" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1544,22 +1406,19 @@
         <v>0.45200145244598</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D51">
         <v>0.01</v>
       </c>
       <c r="E51">
-        <v>0.45200145244598</v>
-      </c>
-      <c r="F51">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G51" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1567,22 +1426,19 @@
         <v>0.45444664359093001</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52">
         <v>0.01</v>
       </c>
       <c r="E52">
-        <v>0.45444664359093001</v>
-      </c>
-      <c r="F52">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G52" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1590,22 +1446,19 @@
         <v>0.45263537764549</v>
       </c>
       <c r="C53" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D53">
         <v>0.01</v>
       </c>
       <c r="E53">
-        <v>0.45263537764549</v>
-      </c>
-      <c r="F53">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G53" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F53" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1613,22 +1466,19 @@
         <v>0.45236369967460999</v>
       </c>
       <c r="C54" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D54">
         <v>0.01</v>
       </c>
       <c r="E54">
-        <v>0.45236369967460999</v>
-      </c>
-      <c r="F54">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G54" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F54" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1636,22 +1486,19 @@
         <v>0.45263537764549</v>
       </c>
       <c r="C55" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>0.01</v>
       </c>
       <c r="E55">
-        <v>0.45263537764549</v>
-      </c>
-      <c r="F55">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G55" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1659,22 +1506,19 @@
         <v>0.45444664359093001</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56">
         <v>0.01</v>
       </c>
       <c r="E56">
-        <v>0.45444664359093001</v>
-      </c>
-      <c r="F56">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G56" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1682,22 +1526,19 @@
         <v>0.45209202170371998</v>
       </c>
       <c r="C57" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57">
         <v>0.01</v>
       </c>
       <c r="E57">
-        <v>0.45209202170371998</v>
-      </c>
-      <c r="F57">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G57" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1705,22 +1546,19 @@
         <v>0.45417496562004001</v>
       </c>
       <c r="C58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <v>0.01</v>
       </c>
       <c r="E58">
-        <v>0.45417496562004001</v>
-      </c>
-      <c r="F58">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G58" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1728,22 +1566,19 @@
         <v>0.45145806670188998</v>
       </c>
       <c r="C59" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59">
         <v>0.01</v>
       </c>
       <c r="E59">
-        <v>0.45145806670188998</v>
-      </c>
-      <c r="F59">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G59" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F59" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1751,22 +1586,19 @@
         <v>0.45471835136414002</v>
       </c>
       <c r="C60" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D60">
         <v>0.01</v>
       </c>
       <c r="E60">
-        <v>0.45471835136414002</v>
-      </c>
-      <c r="F60">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1774,22 +1606,19 @@
         <v>0.45145806670188998</v>
       </c>
       <c r="C61" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D61">
         <v>0.01</v>
       </c>
       <c r="E61">
-        <v>0.45145806670188998</v>
-      </c>
-      <c r="F61">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G61" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F61" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1797,22 +1626,19 @@
         <v>0.45607680082321</v>
       </c>
       <c r="C62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D62">
         <v>1E-3</v>
       </c>
       <c r="E62">
-        <v>0.45607680082321</v>
-      </c>
-      <c r="F62">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G62" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F62" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1820,22 +1646,19 @@
         <v>0.44973737001419001</v>
       </c>
       <c r="C63" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D63">
         <v>1E-3</v>
       </c>
       <c r="E63">
-        <v>0.44973737001419001</v>
-      </c>
-      <c r="F63">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G63" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1843,22 +1666,19 @@
         <v>0.45354101061821001</v>
       </c>
       <c r="C64" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D64">
         <v>1E-3</v>
       </c>
       <c r="E64">
-        <v>0.45354101061821001</v>
-      </c>
-      <c r="F64">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G64" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F64" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1866,22 +1686,19 @@
         <v>0.45417496562004001</v>
       </c>
       <c r="C65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D65">
         <v>1E-3</v>
       </c>
       <c r="E65">
-        <v>0.45417496562004001</v>
-      </c>
-      <c r="F65">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G65" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F65" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1889,22 +1706,19 @@
         <v>0.45245426893233998</v>
       </c>
       <c r="C66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D66">
         <v>1E-3</v>
       </c>
       <c r="E66">
-        <v>0.45245426893233998</v>
-      </c>
-      <c r="F66">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G66" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F66" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1912,22 +1726,19 @@
         <v>0.45354101061821001</v>
       </c>
       <c r="C67" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D67">
         <v>1E-3</v>
       </c>
       <c r="E67">
-        <v>0.45354101061821001</v>
-      </c>
-      <c r="F67">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G67" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F67" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1935,22 +1746,19 @@
         <v>0.45064300298691001</v>
       </c>
       <c r="C68" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D68">
         <v>1E-3</v>
       </c>
       <c r="E68">
-        <v>0.45064300298691001</v>
-      </c>
-      <c r="F68">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G68" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F68" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1958,22 +1766,19 @@
         <v>0.45444664359093001</v>
       </c>
       <c r="C69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69">
         <v>1E-3</v>
       </c>
       <c r="E69">
-        <v>0.45444664359093001</v>
-      </c>
-      <c r="F69">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G69" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F69" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1981,22 +1786,19 @@
         <v>0.45200145244598</v>
       </c>
       <c r="C70" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D70">
         <v>1E-3</v>
       </c>
       <c r="E70">
-        <v>0.45200145244598</v>
-      </c>
-      <c r="F70">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G70" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F70" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2004,22 +1806,19 @@
         <v>0.45390328764915</v>
       </c>
       <c r="C71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D71">
         <v>1E-3</v>
       </c>
       <c r="E71">
-        <v>0.45390328764915</v>
-      </c>
-      <c r="F71">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G71" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2027,22 +1826,19 @@
         <v>0.45281651616096003</v>
       </c>
       <c r="C72" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D72">
         <v>1E-3</v>
       </c>
       <c r="E72">
-        <v>0.45281651616096003</v>
-      </c>
-      <c r="F72">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G72" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F72" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2050,22 +1846,19 @@
         <v>0.45281651616096003</v>
       </c>
       <c r="C73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D73">
         <v>1E-3</v>
       </c>
       <c r="E73">
-        <v>0.45281651616096003</v>
-      </c>
-      <c r="F73">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G73" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F73" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2073,22 +1866,19 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D74">
         <v>1E-3</v>
       </c>
       <c r="E74">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F74">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G74" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F74" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2096,22 +1886,19 @@
         <v>0.45200145244598</v>
       </c>
       <c r="C75" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D75">
         <v>1E-3</v>
       </c>
       <c r="E75">
-        <v>0.45200145244598</v>
-      </c>
-      <c r="F75">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G75" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F75" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2119,22 +1906,19 @@
         <v>0.45182031393050998</v>
       </c>
       <c r="C76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D76">
         <v>1E-3</v>
       </c>
       <c r="E76">
-        <v>0.45182031393050998</v>
-      </c>
-      <c r="F76">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G76" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F76" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2142,22 +1926,19 @@
         <v>0.45517116785049</v>
       </c>
       <c r="C77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D77">
         <v>1E-3</v>
       </c>
       <c r="E77">
-        <v>0.45517116785049</v>
-      </c>
-      <c r="F77">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G77" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F77" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2165,22 +1946,19 @@
         <v>0.45471835136414002</v>
       </c>
       <c r="C78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D78">
         <v>1E-3</v>
       </c>
       <c r="E78">
-        <v>0.45471835136414002</v>
-      </c>
-      <c r="F78">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G78" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F78" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2188,22 +1966,19 @@
         <v>0.44955623149871998</v>
       </c>
       <c r="C79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D79">
         <v>1E-3</v>
       </c>
       <c r="E79">
-        <v>0.44955623149871998</v>
-      </c>
-      <c r="F79">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G79" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F79" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2211,22 +1986,19 @@
         <v>0.45408439636230002</v>
       </c>
       <c r="C80" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D80">
         <v>1E-3</v>
       </c>
       <c r="E80">
-        <v>0.45408439636230002</v>
-      </c>
-      <c r="F80">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G80" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F80" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2234,22 +2006,19 @@
         <v>0.45281651616096003</v>
       </c>
       <c r="C81" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D81">
         <v>1E-3</v>
       </c>
       <c r="E81">
-        <v>0.45281651616096003</v>
-      </c>
-      <c r="F81">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G81" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F81" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2257,22 +2026,19 @@
         <v>0.45272594690322998</v>
       </c>
       <c r="C82" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D82">
         <v>1E-3</v>
       </c>
       <c r="E82">
-        <v>0.45272594690322998</v>
-      </c>
-      <c r="F82">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G82" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2280,22 +2046,19 @@
         <v>0.45354101061821001</v>
       </c>
       <c r="C83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D83">
         <v>1E-3</v>
       </c>
       <c r="E83">
-        <v>0.45354101061821001</v>
-      </c>
-      <c r="F83">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G83" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F83" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2303,22 +2066,19 @@
         <v>0.45218256115913003</v>
       </c>
       <c r="C84" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D84">
         <v>1E-3</v>
       </c>
       <c r="E84">
-        <v>0.45218256115913003</v>
-      </c>
-      <c r="F84">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G84" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2326,22 +2086,19 @@
         <v>0.45290708541870001</v>
       </c>
       <c r="C85" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D85">
         <v>1E-3</v>
       </c>
       <c r="E85">
-        <v>0.45290708541870001</v>
-      </c>
-      <c r="F85">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G85" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F85" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2349,22 +2106,19 @@
         <v>0.45480892062187001</v>
       </c>
       <c r="C86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86">
         <v>1E-3</v>
       </c>
       <c r="E86">
-        <v>0.45480892062187001</v>
-      </c>
-      <c r="F86">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G86" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F86" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2372,22 +2126,19 @@
         <v>0.45100525021553001</v>
       </c>
       <c r="C87" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D87">
         <v>1E-3</v>
       </c>
       <c r="E87">
-        <v>0.45100525021553001</v>
-      </c>
-      <c r="F87">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G87" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F87" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2395,22 +2146,19 @@
         <v>0.45326933264732</v>
       </c>
       <c r="C88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D88">
         <v>1E-3</v>
       </c>
       <c r="E88">
-        <v>0.45326933264732</v>
-      </c>
-      <c r="F88">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G88" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F88" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2418,22 +2166,19 @@
         <v>0.45118638873099998</v>
       </c>
       <c r="C89" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D89">
         <v>1E-3</v>
       </c>
       <c r="E89">
-        <v>0.45118638873099998</v>
-      </c>
-      <c r="F89">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G89" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>88</v>
       </c>
@@ -2441,22 +2186,19 @@
         <v>0.45535227656364002</v>
       </c>
       <c r="C90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D90">
         <v>1E-3</v>
       </c>
       <c r="E90">
-        <v>0.45535227656364002</v>
-      </c>
-      <c r="F90">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G90" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>89</v>
       </c>
@@ -2464,22 +2206,19 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C91" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D91">
         <v>1E-3</v>
       </c>
       <c r="E91">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F91">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G91" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F91" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>90</v>
       </c>
@@ -2487,22 +2226,19 @@
         <v>0.45218256115913003</v>
       </c>
       <c r="C92" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D92">
         <v>1E-3</v>
       </c>
       <c r="E92">
-        <v>0.45218256115913003</v>
-      </c>
-      <c r="F92">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G92" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>91</v>
       </c>
@@ -2510,22 +2246,19 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C93" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D93">
         <v>1E-3</v>
       </c>
       <c r="E93">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F93">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G93" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>92</v>
       </c>
@@ -2533,22 +2266,19 @@
         <v>0.45453721284866</v>
       </c>
       <c r="C94" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D94">
         <v>1E-3</v>
       </c>
       <c r="E94">
-        <v>0.45453721284866</v>
-      </c>
-      <c r="F94">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G94" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F94" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>93</v>
       </c>
@@ -2556,22 +2286,19 @@
         <v>0.45136749744415</v>
       </c>
       <c r="C95" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D95">
         <v>1E-3</v>
       </c>
       <c r="E95">
-        <v>0.45136749744415</v>
-      </c>
-      <c r="F95">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G95" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F95" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>94</v>
       </c>
@@ -2579,22 +2306,19 @@
         <v>0.45281651616096003</v>
       </c>
       <c r="C96" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D96">
         <v>1E-3</v>
       </c>
       <c r="E96">
-        <v>0.45281651616096003</v>
-      </c>
-      <c r="F96">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G96" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F96" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>95</v>
       </c>
@@ -2602,22 +2326,19 @@
         <v>0.45182031393050998</v>
       </c>
       <c r="C97" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D97">
         <v>1E-3</v>
       </c>
       <c r="E97">
-        <v>0.45182031393050998</v>
-      </c>
-      <c r="F97">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G97" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F97" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>96</v>
       </c>
@@ -2625,22 +2346,19 @@
         <v>0.45544284582138</v>
       </c>
       <c r="C98" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D98">
         <v>1E-3</v>
       </c>
       <c r="E98">
-        <v>0.45544284582138</v>
-      </c>
-      <c r="F98">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G98" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F98" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>97</v>
       </c>
@@ -2648,22 +2366,19 @@
         <v>0.45118638873099998</v>
       </c>
       <c r="C99" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D99">
         <v>1E-3</v>
       </c>
       <c r="E99">
-        <v>0.45118638873099998</v>
-      </c>
-      <c r="F99">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G99" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F99" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>98</v>
       </c>
@@ -2671,22 +2386,19 @@
         <v>0.45326933264732</v>
       </c>
       <c r="C100" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D100">
         <v>1E-3</v>
       </c>
       <c r="E100">
-        <v>0.45326933264732</v>
-      </c>
-      <c r="F100">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G100" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F100" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>99</v>
       </c>
@@ -2694,22 +2406,19 @@
         <v>0.45326933264732</v>
       </c>
       <c r="C101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D101">
         <v>1E-3</v>
       </c>
       <c r="E101">
-        <v>0.45326933264732</v>
-      </c>
-      <c r="F101">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G101" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F101" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>100</v>
       </c>
@@ -2717,22 +2426,19 @@
         <v>0.45381271839142001</v>
       </c>
       <c r="C102" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D102">
         <v>1E-3</v>
       </c>
       <c r="E102">
-        <v>0.45381271839142001</v>
-      </c>
-      <c r="F102">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G102" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F102" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>101</v>
       </c>
@@ -2740,22 +2446,19 @@
         <v>0.45272594690322998</v>
       </c>
       <c r="C103" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D103">
         <v>1E-3</v>
       </c>
       <c r="E103">
-        <v>0.45272594690322998</v>
-      </c>
-      <c r="F103">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G103" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F103" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>102</v>
       </c>
@@ -2763,22 +2466,19 @@
         <v>0.45326933264732</v>
       </c>
       <c r="C104" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D104">
         <v>1E-3</v>
       </c>
       <c r="E104">
-        <v>0.45326933264732</v>
-      </c>
-      <c r="F104">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G104" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F104" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>103</v>
       </c>
@@ -2786,22 +2486,19 @@
         <v>0.45308819413184998</v>
       </c>
       <c r="C105" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D105">
         <v>1E-3</v>
       </c>
       <c r="E105">
-        <v>0.45308819413184998</v>
-      </c>
-      <c r="F105">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G105" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F105" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>104</v>
       </c>
@@ -2809,22 +2506,19 @@
         <v>0.45118638873099998</v>
       </c>
       <c r="C106" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D106">
         <v>1E-3</v>
       </c>
       <c r="E106">
-        <v>0.45118638873099998</v>
-      </c>
-      <c r="F106">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G106" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>105</v>
       </c>
@@ -2832,22 +2526,19 @@
         <v>0.45308819413184998</v>
       </c>
       <c r="C107" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D107">
         <v>1E-3</v>
       </c>
       <c r="E107">
-        <v>0.45308819413184998</v>
-      </c>
-      <c r="F107">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G107" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F107" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>106</v>
       </c>
@@ -2855,22 +2546,19 @@
         <v>0.45272594690322998</v>
       </c>
       <c r="C108" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D108">
         <v>1E-3</v>
       </c>
       <c r="E108">
-        <v>0.45272594690322998</v>
-      </c>
-      <c r="F108">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G108" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>107</v>
       </c>
@@ -2878,22 +2566,19 @@
         <v>0.45263537764549</v>
       </c>
       <c r="C109" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D109">
         <v>1E-3</v>
       </c>
       <c r="E109">
-        <v>0.45263537764549</v>
-      </c>
-      <c r="F109">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G109" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F109" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>108</v>
       </c>
@@ -2901,22 +2586,19 @@
         <v>0.45471835136414002</v>
       </c>
       <c r="C110" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D110">
         <v>1E-3</v>
       </c>
       <c r="E110">
-        <v>0.45471835136414002</v>
-      </c>
-      <c r="F110">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G110" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F110" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>109</v>
       </c>
@@ -2924,22 +2606,19 @@
         <v>0.45236369967460999</v>
       </c>
       <c r="C111" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D111">
         <v>1E-3</v>
       </c>
       <c r="E111">
-        <v>0.45236369967460999</v>
-      </c>
-      <c r="F111">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G111" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F111" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>110</v>
       </c>
@@ -2947,22 +2626,19 @@
         <v>0.45326933264732</v>
       </c>
       <c r="C112" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D112">
         <v>1E-3</v>
       </c>
       <c r="E112">
-        <v>0.45326933264732</v>
-      </c>
-      <c r="F112">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G112" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>111</v>
       </c>
@@ -2970,22 +2646,19 @@
         <v>0.45272594690322998</v>
       </c>
       <c r="C113" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D113">
         <v>1E-3</v>
       </c>
       <c r="E113">
-        <v>0.45272594690322998</v>
-      </c>
-      <c r="F113">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G113" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F113" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>112</v>
       </c>
@@ -2993,22 +2666,19 @@
         <v>0.45263537764549</v>
       </c>
       <c r="C114" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D114">
         <v>1E-3</v>
       </c>
       <c r="E114">
-        <v>0.45263537764549</v>
-      </c>
-      <c r="F114">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G114" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F114" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>113</v>
       </c>
@@ -3016,22 +2686,19 @@
         <v>0.45182031393050998</v>
       </c>
       <c r="C115" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D115">
         <v>1E-3</v>
       </c>
       <c r="E115">
-        <v>0.45182031393050998</v>
-      </c>
-      <c r="F115">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G115" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F115" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>114</v>
       </c>
@@ -3039,22 +2706,19 @@
         <v>0.45571455359459001</v>
       </c>
       <c r="C116" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D116">
         <v>1E-3</v>
       </c>
       <c r="E116">
-        <v>0.45571455359459001</v>
-      </c>
-      <c r="F116">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G116" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F116" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>115</v>
       </c>
@@ -3062,22 +2726,19 @@
         <v>0.45227313041687001</v>
       </c>
       <c r="C117" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D117">
         <v>1E-3</v>
       </c>
       <c r="E117">
-        <v>0.45227313041687001</v>
-      </c>
-      <c r="F117">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G117" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F117" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>116</v>
       </c>
@@ -3085,22 +2746,19 @@
         <v>0.45182031393050998</v>
       </c>
       <c r="C118" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D118">
         <v>1E-3</v>
       </c>
       <c r="E118">
-        <v>0.45182031393050998</v>
-      </c>
-      <c r="F118">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G118" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F118" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>117</v>
       </c>
@@ -3108,22 +2766,19 @@
         <v>0.45381271839142001</v>
       </c>
       <c r="C119" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D119">
         <v>1E-3</v>
       </c>
       <c r="E119">
-        <v>0.45381271839142001</v>
-      </c>
-      <c r="F119">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G119" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F119" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>118</v>
       </c>
@@ -3131,22 +2786,19 @@
         <v>0.45335990190505998</v>
       </c>
       <c r="C120" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D120">
         <v>1E-3</v>
       </c>
       <c r="E120">
-        <v>0.45335990190505998</v>
-      </c>
-      <c r="F120">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G120" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F120" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>119</v>
       </c>
@@ -3154,22 +2806,19 @@
         <v>0.45335990190505998</v>
       </c>
       <c r="C121" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D121">
         <v>1E-3</v>
       </c>
       <c r="E121">
-        <v>0.45335990190505998</v>
-      </c>
-      <c r="F121">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G121" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F121" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>120</v>
       </c>
@@ -3177,22 +2826,19 @@
         <v>0.45172974467277999</v>
       </c>
       <c r="C122" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D122">
         <v>1E-3</v>
       </c>
       <c r="E122">
-        <v>0.45172974467277999</v>
-      </c>
-      <c r="F122">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G122" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F122" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>121</v>
       </c>
@@ -3200,22 +2846,19 @@
         <v>0.45127692818642001</v>
       </c>
       <c r="C123" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D123">
         <v>1E-3</v>
       </c>
       <c r="E123">
-        <v>0.45127692818642001</v>
-      </c>
-      <c r="F123">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G123" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F123" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>122</v>
       </c>
@@ -3223,22 +2866,19 @@
         <v>0.45517116785049</v>
       </c>
       <c r="C124" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D124">
         <v>1E-3</v>
       </c>
       <c r="E124">
-        <v>0.45517116785049</v>
-      </c>
-      <c r="F124">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G124" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F124" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>123</v>
       </c>
@@ -3246,22 +2886,19 @@
         <v>0.45272594690322998</v>
       </c>
       <c r="C125" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D125">
         <v>1E-3</v>
       </c>
       <c r="E125">
-        <v>0.45272594690322998</v>
-      </c>
-      <c r="F125">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G125" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F125" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>124</v>
       </c>
@@ -3269,22 +2906,19 @@
         <v>0.45326933264732</v>
       </c>
       <c r="C126" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D126">
         <v>1E-3</v>
       </c>
       <c r="E126">
-        <v>0.45326933264732</v>
-      </c>
-      <c r="F126">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G126" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F126" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>125</v>
       </c>
@@ -3292,22 +2926,19 @@
         <v>0.45290708541870001</v>
       </c>
       <c r="C127" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D127">
         <v>1E-3</v>
       </c>
       <c r="E127">
-        <v>0.45290708541870001</v>
-      </c>
-      <c r="F127">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G127" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F127" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>126</v>
       </c>
@@ -3315,22 +2946,19 @@
         <v>0.45381271839142001</v>
       </c>
       <c r="C128" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D128">
         <v>1E-3</v>
       </c>
       <c r="E128">
-        <v>0.45381271839142001</v>
-      </c>
-      <c r="F128">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G128" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F128" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>127</v>
       </c>
@@ -3338,22 +2966,19 @@
         <v>0.45055243372916998</v>
       </c>
       <c r="C129" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D129">
         <v>1E-3</v>
       </c>
       <c r="E129">
-        <v>0.45055243372916998</v>
-      </c>
-      <c r="F129">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G129" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F129" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>128</v>
       </c>
@@ -3361,22 +2986,19 @@
         <v>0.45444664359093001</v>
       </c>
       <c r="C130" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D130">
         <v>1E-3</v>
       </c>
       <c r="E130">
-        <v>0.45444664359093001</v>
-      </c>
-      <c r="F130">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G130" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F130" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>129</v>
       </c>
@@ -3384,22 +3006,19 @@
         <v>0.45499002933501997</v>
       </c>
       <c r="C131" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D131">
         <v>1E-3</v>
       </c>
       <c r="E131">
-        <v>0.45499002933501997</v>
-      </c>
-      <c r="F131">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G131" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F131" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>130</v>
       </c>
@@ -3407,22 +3026,19 @@
         <v>0.45028075575829002</v>
       </c>
       <c r="C132" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D132">
         <v>1E-3</v>
       </c>
       <c r="E132">
-        <v>0.45028075575829002</v>
-      </c>
-      <c r="F132">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G132" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F132" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>131</v>
       </c>
@@ -3430,22 +3046,19 @@
         <v>0.45245426893233998</v>
       </c>
       <c r="C133" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D133">
         <v>1E-3</v>
       </c>
       <c r="E133">
-        <v>0.45245426893233998</v>
-      </c>
-      <c r="F133">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G133" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F133" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>132</v>
       </c>
@@ -3453,22 +3066,19 @@
         <v>0.45508059859276001</v>
       </c>
       <c r="C134" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D134">
         <v>1E-3</v>
       </c>
       <c r="E134">
-        <v>0.45508059859276001</v>
-      </c>
-      <c r="F134">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G134" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F134" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>133</v>
       </c>
@@ -3476,22 +3086,19 @@
         <v>0.45218256115913003</v>
       </c>
       <c r="C135" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D135">
         <v>1E-3</v>
       </c>
       <c r="E135">
-        <v>0.45218256115913003</v>
-      </c>
-      <c r="F135">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G135" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F135" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>134</v>
       </c>
@@ -3499,22 +3106,19 @@
         <v>0.45444664359093001</v>
       </c>
       <c r="C136" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D136">
         <v>1E-3</v>
       </c>
       <c r="E136">
-        <v>0.45444664359093001</v>
-      </c>
-      <c r="F136">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G136" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F136" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>135</v>
       </c>
@@ -3522,22 +3126,19 @@
         <v>0.45191088318825001</v>
       </c>
       <c r="C137" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D137">
         <v>1E-3</v>
       </c>
       <c r="E137">
-        <v>0.45191088318825001</v>
-      </c>
-      <c r="F137">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G137" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F137" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>136</v>
       </c>
@@ -3545,22 +3146,19 @@
         <v>0.45182031393050998</v>
       </c>
       <c r="C138" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D138">
         <v>1E-3</v>
       </c>
       <c r="E138">
-        <v>0.45182031393050998</v>
-      </c>
-      <c r="F138">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G138" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F138" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>137</v>
       </c>
@@ -3568,22 +3166,19 @@
         <v>0.45218256115913003</v>
       </c>
       <c r="C139" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D139">
         <v>1E-3</v>
       </c>
       <c r="E139">
-        <v>0.45218256115913003</v>
-      </c>
-      <c r="F139">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G139" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F139" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>138</v>
       </c>
@@ -3591,22 +3186,19 @@
         <v>0.45526173710822998</v>
       </c>
       <c r="C140" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D140">
         <v>1E-3</v>
       </c>
       <c r="E140">
-        <v>0.45526173710822998</v>
-      </c>
-      <c r="F140">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G140" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F140" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>139</v>
       </c>
@@ -3614,22 +3206,19 @@
         <v>0.45136749744415</v>
       </c>
       <c r="C141" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D141">
         <v>1E-3</v>
       </c>
       <c r="E141">
-        <v>0.45136749744415</v>
-      </c>
-      <c r="F141">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G141" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F141" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>140</v>
       </c>
@@ -3637,22 +3226,19 @@
         <v>0.45326933264732</v>
       </c>
       <c r="C142" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D142">
         <v>1E-3</v>
       </c>
       <c r="E142">
-        <v>0.45326933264732</v>
-      </c>
-      <c r="F142">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G142" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F142" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>141</v>
       </c>
@@ -3660,22 +3246,19 @@
         <v>0.45281651616096003</v>
       </c>
       <c r="C143" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D143">
         <v>1E-3</v>
       </c>
       <c r="E143">
-        <v>0.45281651616096003</v>
-      </c>
-      <c r="F143">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G143" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F143" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>142</v>
       </c>
@@ -3683,22 +3266,19 @@
         <v>0.45508059859276001</v>
       </c>
       <c r="C144" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D144">
         <v>1E-3</v>
       </c>
       <c r="E144">
-        <v>0.45508059859276001</v>
-      </c>
-      <c r="F144">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G144" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F144" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>143</v>
       </c>
@@ -3706,22 +3286,19 @@
         <v>0.45009961724281</v>
       </c>
       <c r="C145" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D145">
         <v>1E-3</v>
       </c>
       <c r="E145">
-        <v>0.45009961724281</v>
-      </c>
-      <c r="F145">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G145" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F145" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>144</v>
       </c>
@@ -3729,22 +3306,19 @@
         <v>0.45480892062187001</v>
       </c>
       <c r="C146" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D146">
         <v>1E-3</v>
       </c>
       <c r="E146">
-        <v>0.45480892062187001</v>
-      </c>
-      <c r="F146">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G146" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F146" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>145</v>
       </c>
@@ -3752,22 +3326,19 @@
         <v>0.45209202170371998</v>
       </c>
       <c r="C147" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D147">
         <v>1E-3</v>
       </c>
       <c r="E147">
-        <v>0.45209202170371998</v>
-      </c>
-      <c r="F147">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G147" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F147" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>146</v>
       </c>
@@ -3775,22 +3346,19 @@
         <v>0.45254483819008001</v>
       </c>
       <c r="C148" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D148">
         <v>1E-3</v>
       </c>
       <c r="E148">
-        <v>0.45254483819008001</v>
-      </c>
-      <c r="F148">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G148" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F148" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>147</v>
       </c>
@@ -3798,22 +3366,19 @@
         <v>0.45598623156548002</v>
       </c>
       <c r="C149" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D149">
         <v>1E-3</v>
       </c>
       <c r="E149">
-        <v>0.45598623156548002</v>
-      </c>
-      <c r="F149">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G149" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F149" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>148</v>
       </c>
@@ -3821,22 +3386,19 @@
         <v>0.44928455352782998</v>
       </c>
       <c r="C150" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D150">
         <v>1E-3</v>
       </c>
       <c r="E150">
-        <v>0.44928455352782998</v>
-      </c>
-      <c r="F150">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G150" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F150" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>149</v>
       </c>
@@ -3844,22 +3406,19 @@
         <v>0.45607680082321</v>
       </c>
       <c r="C151" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D151">
         <v>1E-3</v>
       </c>
       <c r="E151">
-        <v>0.45607680082321</v>
-      </c>
-      <c r="F151">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G151" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F151" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>150</v>
       </c>
@@ -3867,22 +3426,19 @@
         <v>0.45100525021553001</v>
       </c>
       <c r="C152" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D152">
         <v>1E-3</v>
       </c>
       <c r="E152">
-        <v>0.45100525021553001</v>
-      </c>
-      <c r="F152">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G152" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F152" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>151</v>
       </c>
@@ -3890,22 +3446,19 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C153" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D153">
         <v>1E-3</v>
       </c>
       <c r="E153">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F153">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G153" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F153" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>152</v>
       </c>
@@ -3913,22 +3466,19 @@
         <v>0.45499002933501997</v>
       </c>
       <c r="C154" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D154">
         <v>1E-3</v>
       </c>
       <c r="E154">
-        <v>0.45499002933501997</v>
-      </c>
-      <c r="F154">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G154" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F154" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>153</v>
       </c>
@@ -3936,22 +3486,19 @@
         <v>0.45046186447143999</v>
       </c>
       <c r="C155" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D155">
         <v>1E-3</v>
       </c>
       <c r="E155">
-        <v>0.45046186447143999</v>
-      </c>
-      <c r="F155">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G155" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F155" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>154</v>
       </c>
@@ -3959,22 +3506,19 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C156" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D156">
         <v>1E-3</v>
       </c>
       <c r="E156">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F156">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G156" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F156" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>155</v>
       </c>
@@ -3982,22 +3526,19 @@
         <v>0.45535227656364002</v>
       </c>
       <c r="C157" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D157">
         <v>1E-3</v>
       </c>
       <c r="E157">
-        <v>0.45535227656364002</v>
-      </c>
-      <c r="F157">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G157" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F157" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>156</v>
       </c>
@@ -4005,22 +3546,19 @@
         <v>0.45019018650054998</v>
       </c>
       <c r="C158" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D158">
         <v>1E-3</v>
       </c>
       <c r="E158">
-        <v>0.45019018650054998</v>
-      </c>
-      <c r="F158">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G158" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F158" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>157</v>
       </c>
@@ -4028,22 +3566,19 @@
         <v>0.45390328764915</v>
       </c>
       <c r="C159" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D159">
         <v>1E-3</v>
       </c>
       <c r="E159">
-        <v>0.45390328764915</v>
-      </c>
-      <c r="F159">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G159" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F159" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>158</v>
       </c>
@@ -4051,22 +3586,19 @@
         <v>0.45209202170371998</v>
       </c>
       <c r="C160" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D160">
         <v>1E-3</v>
       </c>
       <c r="E160">
-        <v>0.45209202170371998</v>
-      </c>
-      <c r="F160">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G160" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F160" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>159</v>
       </c>
@@ -4074,22 +3606,19 @@
         <v>0.45526173710822998</v>
       </c>
       <c r="C161" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D161">
         <v>1E-3</v>
       </c>
       <c r="E161">
-        <v>0.45526173710822998</v>
-      </c>
-      <c r="F161">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G161" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F161" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>160</v>
       </c>
@@ -4097,22 +3626,19 @@
         <v>0.45109581947326999</v>
       </c>
       <c r="C162" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D162">
         <v>1E-3</v>
       </c>
       <c r="E162">
-        <v>0.45109581947326999</v>
-      </c>
-      <c r="F162">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G162" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F162" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>161</v>
       </c>
@@ -4120,22 +3646,19 @@
         <v>0.45335990190505998</v>
       </c>
       <c r="C163" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D163">
         <v>1E-3</v>
       </c>
       <c r="E163">
-        <v>0.45335990190505998</v>
-      </c>
-      <c r="F163">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G163" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F163" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>162</v>
       </c>
@@ -4143,22 +3666,19 @@
         <v>0.45218256115913003</v>
       </c>
       <c r="C164" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D164">
         <v>1E-3</v>
       </c>
       <c r="E164">
-        <v>0.45218256115913003</v>
-      </c>
-      <c r="F164">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G164" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F164" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>163</v>
       </c>
@@ -4166,22 +3686,19 @@
         <v>0.45345047116280002</v>
       </c>
       <c r="C165" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D165">
         <v>1E-3</v>
       </c>
       <c r="E165">
-        <v>0.45345047116280002</v>
-      </c>
-      <c r="F165">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G165" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F165" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>164</v>
       </c>
@@ -4189,22 +3706,19 @@
         <v>0.45281651616096003</v>
       </c>
       <c r="C166" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D166">
         <v>1E-3</v>
       </c>
       <c r="E166">
-        <v>0.45281651616096003</v>
-      </c>
-      <c r="F166">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G166" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F166" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>165</v>
       </c>
@@ -4212,22 +3726,19 @@
         <v>0.45399382710456998</v>
       </c>
       <c r="C167" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D167">
         <v>1E-3</v>
       </c>
       <c r="E167">
-        <v>0.45399382710456998</v>
-      </c>
-      <c r="F167">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G167" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F167" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>166</v>
       </c>
@@ -4235,22 +3746,19 @@
         <v>0.45245426893233998</v>
       </c>
       <c r="C168" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D168">
         <v>1E-3</v>
       </c>
       <c r="E168">
-        <v>0.45245426893233998</v>
-      </c>
-      <c r="F168">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G168" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F168" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>167</v>
       </c>
@@ -4258,22 +3766,19 @@
         <v>0.45254483819008001</v>
       </c>
       <c r="C169" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D169">
         <v>1E-3</v>
       </c>
       <c r="E169">
-        <v>0.45254483819008001</v>
-      </c>
-      <c r="F169">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G169" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F169" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>168</v>
       </c>
@@ -4281,22 +3786,19 @@
         <v>0.45544284582138</v>
       </c>
       <c r="C170" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D170">
         <v>1E-3</v>
       </c>
       <c r="E170">
-        <v>0.45544284582138</v>
-      </c>
-      <c r="F170">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G170" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F170" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>169</v>
       </c>
@@ -4304,22 +3806,19 @@
         <v>0.45136749744415</v>
       </c>
       <c r="C171" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D171">
         <v>1E-3</v>
       </c>
       <c r="E171">
-        <v>0.45136749744415</v>
-      </c>
-      <c r="F171">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G171" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F171" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>170</v>
       </c>
@@ -4327,22 +3826,19 @@
         <v>0.45236369967460999</v>
       </c>
       <c r="C172" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D172">
         <v>1E-3</v>
       </c>
       <c r="E172">
-        <v>0.45236369967460999</v>
-      </c>
-      <c r="F172">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G172" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F172" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>171</v>
       </c>
@@ -4350,22 +3846,19 @@
         <v>0.45462778210639998</v>
       </c>
       <c r="C173" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D173">
         <v>1E-3</v>
       </c>
       <c r="E173">
-        <v>0.45462778210639998</v>
-      </c>
-      <c r="F173">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G173" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>172</v>
       </c>
@@ -4373,22 +3866,19 @@
         <v>0.45236369967460999</v>
       </c>
       <c r="C174" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D174">
         <v>1E-3</v>
       </c>
       <c r="E174">
-        <v>0.45236369967460999</v>
-      </c>
-      <c r="F174">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G174" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F174" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>173</v>
       </c>
@@ -4396,22 +3886,19 @@
         <v>0.45091468095779003</v>
       </c>
       <c r="C175" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D175">
         <v>1E-3</v>
       </c>
       <c r="E175">
-        <v>0.45091468095779003</v>
-      </c>
-      <c r="F175">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G175" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F175" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>174</v>
       </c>
@@ -4419,22 +3906,19 @@
         <v>0.45480892062187001</v>
       </c>
       <c r="C176" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D176">
         <v>1E-3</v>
       </c>
       <c r="E176">
-        <v>0.45480892062187001</v>
-      </c>
-      <c r="F176">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G176" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F176" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>175</v>
       </c>
@@ -4442,22 +3926,19 @@
         <v>0.45254483819008001</v>
       </c>
       <c r="C177" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D177">
         <v>1E-3</v>
       </c>
       <c r="E177">
-        <v>0.45254483819008001</v>
-      </c>
-      <c r="F177">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G177" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F177" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>176</v>
       </c>
@@ -4465,22 +3946,19 @@
         <v>0.45263537764549</v>
       </c>
       <c r="C178" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D178">
         <v>1E-3</v>
       </c>
       <c r="E178">
-        <v>0.45263537764549</v>
-      </c>
-      <c r="F178">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G178" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F178" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>177</v>
       </c>
@@ -4488,22 +3966,19 @@
         <v>0.45489946007728999</v>
       </c>
       <c r="C179" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D179">
         <v>1E-3</v>
       </c>
       <c r="E179">
-        <v>0.45489946007728999</v>
-      </c>
-      <c r="F179">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G179" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F179" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>178</v>
       </c>
@@ -4511,22 +3986,19 @@
         <v>0.45172974467277999</v>
       </c>
       <c r="C180" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D180">
         <v>1E-3</v>
       </c>
       <c r="E180">
-        <v>0.45172974467277999</v>
-      </c>
-      <c r="F180">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G180" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F180" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>179</v>
       </c>
@@ -4534,22 +4006,19 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C181" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D181">
         <v>1E-3</v>
       </c>
       <c r="E181">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F181">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G181" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F181" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>180</v>
       </c>
@@ -4557,22 +4026,19 @@
         <v>0.45372214913367998</v>
       </c>
       <c r="C182" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D182">
         <v>1E-3</v>
       </c>
       <c r="E182">
-        <v>0.45372214913367998</v>
-      </c>
-      <c r="F182">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G182" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F182" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>181</v>
       </c>
@@ -4580,22 +4046,19 @@
         <v>0.45308819413184998</v>
       </c>
       <c r="C183" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D183">
         <v>1E-3</v>
       </c>
       <c r="E183">
-        <v>0.45308819413184998</v>
-      </c>
-      <c r="F183">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G183" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F183" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>182</v>
       </c>
@@ -4603,22 +4066,19 @@
         <v>0.45299765467643999</v>
       </c>
       <c r="C184" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D184">
         <v>1E-3</v>
       </c>
       <c r="E184">
-        <v>0.45299765467643999</v>
-      </c>
-      <c r="F184">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G184" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F184" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>183</v>
       </c>
@@ -4626,22 +4086,19 @@
         <v>0.45444664359093001</v>
       </c>
       <c r="C185" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D185">
         <v>1E-3</v>
       </c>
       <c r="E185">
-        <v>0.45444664359093001</v>
-      </c>
-      <c r="F185">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G185" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F185" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>184</v>
       </c>
@@ -4649,22 +4106,19 @@
         <v>0.45100525021553001</v>
       </c>
       <c r="C186" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D186">
         <v>1E-3</v>
       </c>
       <c r="E186">
-        <v>0.45100525021553001</v>
-      </c>
-      <c r="F186">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G186" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F186" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>185</v>
       </c>
@@ -4672,22 +4126,19 @@
         <v>0.45363157987594999</v>
       </c>
       <c r="C187" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D187">
         <v>1E-3</v>
       </c>
       <c r="E187">
-        <v>0.45363157987594999</v>
-      </c>
-      <c r="F187">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G187" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F187" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>186</v>
       </c>
@@ -4695,22 +4146,19 @@
         <v>0.45136749744415</v>
       </c>
       <c r="C188" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D188">
         <v>1E-3</v>
       </c>
       <c r="E188">
-        <v>0.45136749744415</v>
-      </c>
-      <c r="F188">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G188" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F188" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>187</v>
       </c>
@@ -4718,22 +4166,19 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C189" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D189">
         <v>1E-3</v>
       </c>
       <c r="E189">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F189">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G189" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F189" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>188</v>
       </c>
@@ -4741,22 +4186,19 @@
         <v>0.45118638873099998</v>
       </c>
       <c r="C190" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D190">
         <v>1E-3</v>
       </c>
       <c r="E190">
-        <v>0.45118638873099998</v>
-      </c>
-      <c r="F190">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G190" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F190" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>189</v>
       </c>
@@ -4764,22 +4206,19 @@
         <v>0.45562398433684997</v>
       </c>
       <c r="C191" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D191">
         <v>1E-3</v>
       </c>
       <c r="E191">
-        <v>0.45562398433684997</v>
-      </c>
-      <c r="F191">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G191" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F191" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>190</v>
       </c>
@@ -4787,22 +4226,19 @@
         <v>0.45335990190505998</v>
       </c>
       <c r="C192" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D192">
         <v>1E-3</v>
       </c>
       <c r="E192">
-        <v>0.45335990190505998</v>
-      </c>
-      <c r="F192">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G192" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F192" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>191</v>
       </c>
@@ -4810,22 +4246,19 @@
         <v>0.45263537764549</v>
       </c>
       <c r="C193" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D193">
         <v>1E-3</v>
       </c>
       <c r="E193">
-        <v>0.45263537764549</v>
-      </c>
-      <c r="F193">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G193" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F193" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>192</v>
       </c>
@@ -4833,22 +4266,19 @@
         <v>0.45335990190505998</v>
       </c>
       <c r="C194" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D194">
         <v>1E-3</v>
       </c>
       <c r="E194">
-        <v>0.45335990190505998</v>
-      </c>
-      <c r="F194">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G194" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F194" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>193</v>
       </c>
@@ -4856,22 +4286,19 @@
         <v>0.45408439636230002</v>
       </c>
       <c r="C195" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D195">
         <v>1E-3</v>
       </c>
       <c r="E195">
-        <v>0.45408439636230002</v>
-      </c>
-      <c r="F195">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G195" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F195" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>194</v>
       </c>
@@ -4879,22 +4306,19 @@
         <v>0.45236369967460999</v>
       </c>
       <c r="C196" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D196">
         <v>1E-3</v>
       </c>
       <c r="E196">
-        <v>0.45236369967460999</v>
-      </c>
-      <c r="F196">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G196" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F196" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>195</v>
       </c>
@@ -4902,22 +4326,19 @@
         <v>0.45272594690322998</v>
       </c>
       <c r="C197" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D197">
         <v>1E-3</v>
       </c>
       <c r="E197">
-        <v>0.45272594690322998</v>
-      </c>
-      <c r="F197">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G197" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F197" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>196</v>
       </c>
@@ -4925,22 +4346,19 @@
         <v>0.45145806670188998</v>
       </c>
       <c r="C198" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D198">
         <v>1E-3</v>
       </c>
       <c r="E198">
-        <v>0.45145806670188998</v>
-      </c>
-      <c r="F198">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G198" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F198" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>197</v>
       </c>
@@ -4948,22 +4366,19 @@
         <v>0.45372214913367998</v>
       </c>
       <c r="C199" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D199">
         <v>1E-3</v>
       </c>
       <c r="E199">
-        <v>0.45372214913367998</v>
-      </c>
-      <c r="F199">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G199" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F199" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>198</v>
       </c>
@@ -4971,22 +4386,19 @@
         <v>0.45462778210639998</v>
       </c>
       <c r="C200" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D200">
         <v>1E-3</v>
       </c>
       <c r="E200">
-        <v>0.45462778210639998</v>
-      </c>
-      <c r="F200">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G200" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F200" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>199</v>
       </c>
@@ -4994,19 +4406,16 @@
         <v>0.45317876338959001</v>
       </c>
       <c r="C201" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D201">
         <v>1E-3</v>
       </c>
       <c r="E201">
-        <v>0.45317876338959001</v>
-      </c>
-      <c r="F201">
-        <v>0.45530521869659002</v>
-      </c>
-      <c r="G201" t="s">
-        <v>7</v>
+        <v>0.45530521869659002</v>
+      </c>
+      <c r="F201" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
